--- a/project_tracker_workbook.xlsx
+++ b/project_tracker_workbook.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\COD Last 4\capstone project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\COD Last 4\capstone project\week 10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFE791C-0546-498B-B966-1B29913880BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5C5DED-124F-4B52-837E-7DF042EB2A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{C7E3B102-2D79-404D-96C8-06FB473DFC22}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="134">
   <si>
     <t>Team Members</t>
   </si>
@@ -436,6 +436,15 @@
   </si>
   <si>
     <t>https://github.com/CalebOkrzesik/capstoneprojects/blob/main/JellyFinMoviesApp.docx</t>
+  </si>
+  <si>
+    <t>10/27/2025-10/31/2025</t>
+  </si>
+  <si>
+    <t>I set out to make a command line base game of sudoku which would play the basic game. It would be able to create a game board. Which is 81 squares, and it would populate the whole board. Then it will allow for difficulty to be set by user and it removes the correct amount according to user specified difficulty. It randomly chooses an amount by the difficulty chosen by user between the averages and removes values by difficulty. It allows for user to input values. It also tells them if it is allowed, incorrect, or otherwise.</t>
+  </si>
+  <si>
+    <t>https://github.com/CalebOkrzesik/capstoneprojects/blob/main/sudoku.py</t>
   </si>
 </sst>
 </file>
@@ -583,7 +592,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -605,27 +614,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -663,6 +651,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1555,47 +1567,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13"/>
+      <c r="C2" s="26"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="28"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="12"/>
+      <c r="C7" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1628,11 +1640,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1646,7 +1658,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="12" t="s">
         <v>37</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -1657,7 +1669,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="12" t="s">
         <v>38</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -1668,18 +1680,18 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="12" t="s">
         <v>39</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="19" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="13" t="s">
         <v>40</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -1690,18 +1702,18 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="13" t="s">
         <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="19" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="14" t="s">
         <v>54</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -1712,7 +1724,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="20" t="s">
         <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1723,7 +1735,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="20" t="s">
         <v>58</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1734,7 +1746,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="20" t="s">
         <v>61</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -1783,17 +1795,17 @@
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="9" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="11" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1823,15 +1835,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -1863,7 +1875,7 @@
       <c r="A3" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="16" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -1889,7 +1901,7 @@
       <c r="A4" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="16" t="s">
         <v>74</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -1915,7 +1927,7 @@
       <c r="A5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="16" t="s">
         <v>75</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -1941,7 +1953,7 @@
       <c r="A6" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="18" t="s">
         <v>76</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1967,7 +1979,7 @@
       <c r="A7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="17" t="s">
         <v>77</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1993,7 +2005,7 @@
       <c r="A8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="18" t="s">
         <v>78</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -2019,7 +2031,7 @@
       <c r="A9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="18" t="s">
         <v>79</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -2045,7 +2057,7 @@
       <c r="A10" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="16" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -2071,7 +2083,7 @@
       <c r="A11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="16" t="s">
         <v>83</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -2170,7 +2182,7 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="10" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2182,7 +2194,7 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
-      <c r="H20" s="20" t="s">
+      <c r="H20" s="11" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2194,7 +2206,7 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="18" t="s">
+      <c r="H21" s="9" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2415,10 +2427,10 @@
       <c r="G45" s="4"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
+      <c r="A46" s="15"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
@@ -2447,14 +2459,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -2741,7 +2753,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="30" style="5" customWidth="1"/>
     <col min="3" max="4" width="12.85546875" style="5" customWidth="1"/>
     <col min="5" max="5" width="43.7109375" style="5" customWidth="1"/>
     <col min="6" max="6" width="33.85546875" style="5" customWidth="1"/>
@@ -2772,7 +2784,7 @@
       <c r="A2" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="30">
+      <c r="B2" s="21">
         <v>45915</v>
       </c>
       <c r="C2" s="4">
@@ -2792,7 +2804,7 @@
       <c r="A3" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="21">
         <v>45926</v>
       </c>
       <c r="C3" s="4">
@@ -2812,7 +2824,7 @@
       <c r="A4" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="21">
         <v>45908</v>
       </c>
       <c r="C4" s="4">
@@ -2828,15 +2840,25 @@
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="180" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="4">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -3945,6 +3967,9 @@
       <c r="F142" s="4"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{1448D09F-AB6C-4DEA-98A9-03662F4FC309}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/project_tracker_workbook.xlsx
+++ b/project_tracker_workbook.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\COD Last 4\capstone project\week 10\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\COD Last 4\capstone project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5C5DED-124F-4B52-837E-7DF042EB2A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F42AD7C-3484-47C0-B3AD-15D40623E5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{C7E3B102-2D79-404D-96C8-06FB473DFC22}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="137">
   <si>
     <t>Team Members</t>
   </si>
@@ -445,6 +445,15 @@
   </si>
   <si>
     <t>https://github.com/CalebOkrzesik/capstoneprojects/blob/main/sudoku.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To create a GUI interface for backend code for sudoku to make the game more enjoyable. The GUI will be web based so I have to convert the code to java script. Also styling sheet and index file are necessary as I will be using GitHub pages to launch the website. I added the file to this document as well as uploading them to my git hub repository. The file are index.html, sudoku.js, and index.css. </t>
+  </si>
+  <si>
+    <t>11/3/2025-11/7/2025</t>
+  </si>
+  <si>
+    <t>Tested Connection to Wi-Fi with different type of connection such as cat 5e, cat 6, Wi-Fi 5 as the device only supports older Wi-Fi codec. As well as re starting server. Testing turning on and off different software’s to see if they were throttling it. Tested to see if it was a hardware issue.  I also tried changing the server port for jelly fin and other networking options to see if that was the issue. The list goes on and on of things I tried but those were some of the big things that I tried.</t>
   </si>
 </sst>
 </file>
@@ -653,6 +662,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -673,9 +685,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1567,47 +1576,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
+      <c r="B1" s="24"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="26"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="28"/>
+      <c r="C3" s="29"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1640,11 +1649,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1835,15 +1844,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -2459,14 +2468,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -2856,29 +2865,49 @@
       <c r="E5" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="4">
+        <v>8</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="165" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="4">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -3969,6 +3998,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F5" r:id="rId1" xr:uid="{1448D09F-AB6C-4DEA-98A9-03662F4FC309}"/>
+    <hyperlink ref="F6" r:id="rId2" xr:uid="{26FE712A-D8EB-494B-9C2A-E68FC4221046}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{0F62FE73-393A-4A07-896C-556A4CCE5428}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/project_tracker_workbook.xlsx
+++ b/project_tracker_workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\COD Last 4\capstone project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F42AD7C-3484-47C0-B3AD-15D40623E5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E287333-CE4A-4B4D-8548-36357A7B0158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{C7E3B102-2D79-404D-96C8-06FB473DFC22}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="141">
   <si>
     <t>Team Members</t>
   </si>
@@ -454,6 +454,20 @@
   </si>
   <si>
     <t>Tested Connection to Wi-Fi with different type of connection such as cat 5e, cat 6, Wi-Fi 5 as the device only supports older Wi-Fi codec. As well as re starting server. Testing turning on and off different software’s to see if they were throttling it. Tested to see if it was a hardware issue.  I also tried changing the server port for jelly fin and other networking options to see if that was the issue. The list goes on and on of things I tried but those were some of the big things that I tried.</t>
+  </si>
+  <si>
+    <t>caleb</t>
+  </si>
+  <si>
+    <t>11/10/2025-11/14/2025</t>
+  </si>
+  <si>
+    <t>Clean Gui output of code and ability to check weather in whatever area you want to. It took about 8 hours because the troubler shooting step of getting the sudoku game to still link from there as GitHub is weird when it comes to having multiple file that are under index linked. Weather app linked here
+https://calebokrzesik.github.io/capstoneprojects/weather.html</t>
+  </si>
+  <si>
+    <t>Landing page that links the two apps weather and sudoku. About 1 hour Check out both apps here at my landing page
+https://calebokrzesik.github.io/capstoneprojects/</t>
   </si>
 </sst>
 </file>
@@ -2909,25 +2923,45 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="4">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
@@ -4000,6 +4034,8 @@
     <hyperlink ref="F5" r:id="rId1" xr:uid="{1448D09F-AB6C-4DEA-98A9-03662F4FC309}"/>
     <hyperlink ref="F6" r:id="rId2" xr:uid="{26FE712A-D8EB-494B-9C2A-E68FC4221046}"/>
     <hyperlink ref="F7" r:id="rId3" xr:uid="{0F62FE73-393A-4A07-896C-556A4CCE5428}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{10E1B50E-DCA6-4529-8F65-0ACF3CE5B237}"/>
+    <hyperlink ref="F9" r:id="rId5" xr:uid="{F330F69A-E23C-4D0A-B3B8-115DC23FA645}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/project_tracker_workbook.xlsx
+++ b/project_tracker_workbook.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\COD Last 4\capstone project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\COD Last 4\capstone project\FINAL WEEK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E287333-CE4A-4B4D-8548-36357A7B0158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AA5012-DDD7-466F-963F-7F3EC106176C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{C7E3B102-2D79-404D-96C8-06FB473DFC22}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="146">
   <si>
     <t>Team Members</t>
   </si>
@@ -468,6 +468,21 @@
   <si>
     <t>Landing page that links the two apps weather and sudoku. About 1 hour Check out both apps here at my landing page
 https://calebokrzesik.github.io/capstoneprojects/</t>
+  </si>
+  <si>
+    <t>I had to create space on my server first. So I allocated storage for each VM. Then to create the linux and windows VM I needed there files to set them up. Windows is easy but Linux you have a lot of option to choose from. I ended up choosing ubuntu. Then I had to section of different parts of the CPU ram etc. for each virtual machine. Then once the networking settings and more in depth settings I had both of them up and running. I tested many different things on each such as making sure it recognized the virtual hardware specs. As well as installing and running different programs you would use on each respective VM.</t>
+  </si>
+  <si>
+    <t>11/17/2025-11/21/2025</t>
+  </si>
+  <si>
+    <t>Sudoku solver, I implemented this in python first to see how to make it work. It was quite a bit of work. Then I figured out the gui aspect of it in html. After that I figured out how to transfer my code from python to java scrypt. There werr many challeneges and was the hardest part of my project. I had a lot of toruble getting the algorithims working.</t>
+  </si>
+  <si>
+    <t>11/24/2025-12/5/2025</t>
+  </si>
+  <si>
+    <t>T-10</t>
   </si>
 </sst>
 </file>
@@ -2963,23 +2978,45 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="210" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="B10" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="4">
+        <v>8</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="4">
+        <v>17</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
@@ -4036,6 +4073,8 @@
     <hyperlink ref="F7" r:id="rId3" xr:uid="{0F62FE73-393A-4A07-896C-556A4CCE5428}"/>
     <hyperlink ref="F8" r:id="rId4" xr:uid="{10E1B50E-DCA6-4529-8F65-0ACF3CE5B237}"/>
     <hyperlink ref="F9" r:id="rId5" xr:uid="{F330F69A-E23C-4D0A-B3B8-115DC23FA645}"/>
+    <hyperlink ref="F10" r:id="rId6" xr:uid="{A0C49C1D-7B9F-46E5-9B7D-38DDD4B4683A}"/>
+    <hyperlink ref="F11" r:id="rId7" xr:uid="{00945A99-16C1-4998-A039-B410D8813C91}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
